--- a/Project.xlsx
+++ b/Project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arthitpuna\manpower_dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08BF9923-25BF-4FF7-ABFC-BA43A83909DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31F0BF26-7AF5-4E20-A3C4-EF4BC415B258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3648,8 +3648,8 @@
       <c r="AC4" s="144" t="s">
         <v>10</v>
       </c>
-      <c r="AD4" s="144" t="s">
-        <v>10</v>
+      <c r="AD4" s="143" t="s">
+        <v>119</v>
       </c>
       <c r="AE4" s="142" t="s">
         <v>116</v>
@@ -9904,7 +9904,7 @@
       </c>
       <c r="AD64" s="344">
         <f t="shared" si="5"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE64" s="344">
         <f t="shared" si="5"/>
